--- a/marketing_forms/012_product_packaging_design_assessment_form--marketing_forms.xlsx
+++ b/marketing_forms/012_product_packaging_design_assessment_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1167,12 +1167,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'bottled'}</t>
+          <t>bottled</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Bottled'}</t>
+          <t>Bottled</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'canned'}</t>
+          <t>canned</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Canned'}</t>
+          <t>Canned</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'simple'}</t>
+          <t>simple</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Simple'}</t>
+          <t>Simple</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'colorful'}</t>
+          <t>colorful</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Colorful'}</t>
+          <t>Colorful</t>
         </is>
       </c>
     </row>
@@ -1285,29 +1285,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'eye_catching'}</t>
+          <t>eye_catching</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Eye Catching'}</t>
+          <t>Eye Catching</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>packaging_design_choices</t>
+          <t>product_packaging_color_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'simple'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Simple'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'red'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Red'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'green'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Green'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1353,29 +1353,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'blue'}</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Blue'}</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>product_packaging_color_choices</t>
+          <t>packaging_size_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'yellow'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Yellow'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Small'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1404,29 +1404,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>packaging_size_choices</t>
+          <t>packaging_weight_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large'}</t>
+          <t>lightweight</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Large'}</t>
+          <t>Lightweight</t>
         </is>
       </c>
     </row>
@@ -1438,29 +1438,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'lightweight'}</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Lightweight'}</t>
+          <t>Heavy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>packaging_weight_choices</t>
+          <t>packaging_materials_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'heavy'}</t>
+          <t>plastic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Heavy'}</t>
+          <t>Plastic</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'plastic'}</t>
+          <t>paper</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Plastic'}</t>
+          <t>Paper</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paper'}</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Paper'}</t>
+          <t>Metal</t>
         </is>
       </c>
     </row>
@@ -1506,29 +1506,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'metal'}</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Metal'}</t>
+          <t>Glass</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>packaging_materials_choices</t>
+          <t>shape_of_packaging_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'glass'}</t>
+          <t>cube</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Glass'}</t>
+          <t>Cube</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cube'}</t>
+          <t>cylinder</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Cube'}</t>
+          <t>Cylinder</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cylinder'}</t>
+          <t>rectangular</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cylinder'}</t>
+          <t>Rectangular</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rectangular'}</t>
+          <t>sphere</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rectangular'}</t>
+          <t>Sphere</t>
         </is>
       </c>
     </row>
@@ -1591,29 +1591,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'sphere'}</t>
+          <t>irregular</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Sphere'}</t>
+          <t>Irregular</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>shape_of_packaging_choices</t>
+          <t>color_of_packaging_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'irregular'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Irregular'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'red'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Red'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'green'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Green'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1659,29 +1659,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'blue'}</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Blue'}</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>color_of_packaging_choices</t>
+          <t>finish_of_packaging_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'yellow'}</t>
+          <t>glossy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Yellow'}</t>
+          <t>Glossy</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'glossy'}</t>
+          <t>matte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Glossy'}</t>
+          <t>Matte</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'matte'}</t>
+          <t>textured</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Matte'}</t>
+          <t>Textured</t>
         </is>
       </c>
     </row>
@@ -1727,29 +1727,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'textured'}</t>
+          <t>embossed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Textured'}</t>
+          <t>Embossed</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>finish_of_packaging_choices</t>
+          <t>packaging_technology_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'embossed'}</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Embossed'}</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'automatic'}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Automatic'}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1778,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'manual'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Manual'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>packaging_technology_choices</t>
+          <t>sustainability_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1829,29 +1829,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sustainability_choices</t>
+          <t>product_packaging_design_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>simple</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Simple</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'simple'}</t>
+          <t>colorful</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Simple'}</t>
+          <t>Colorful</t>
         </is>
       </c>
     </row>
@@ -1880,29 +1880,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'colorful'}</t>
+          <t>eye_catching</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Colorful'}</t>
+          <t>Eye Catching</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>product_packaging_design_choices</t>
+          <t>packaging_sustainability_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'eye_catching'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Eye Catching'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1931,29 +1931,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>packaging_sustainability_choices</t>
+          <t>eco_friendly_materials_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1965,29 +1965,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>eco_friendly_materials_choices</t>
+          <t>packaging_cost_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2016,29 +2016,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>packaging_cost_choices</t>
+          <t>packaging_value_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2050,12 +2050,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2067,29 +2067,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>packaging_value_choices</t>
+          <t>packaging_sustainability_value_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2118,29 +2118,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>packaging_sustainability_value_choices</t>
+          <t>packaging_size_cost_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2169,29 +2169,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>packaging_size_cost_choices</t>
+          <t>packaging_value_cost_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2220,29 +2220,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>packaging_value_cost_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'high'}</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
